--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B160"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55.83203125" customWidth="1" min="1" max="1"/>
@@ -2377,6 +2377,18 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>トップ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55.83203125" customWidth="1" min="1" max="1"/>
@@ -2389,6 +2389,18 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Buy me a coffee</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>コーヒーをおごってください</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B162"/>
+  <dimension ref="A1:B163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55.83203125" customWidth="1" min="1" max="1"/>
@@ -2401,6 +2401,18 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>File header is not standard CGATS (first line does not contain “CGATS” or “ISO28178”)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ファイルヘッダーが標準 CGATS ではありません（1 行目に「CGATS」または「ISO28178」が含まれていません）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -1,32 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Translations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -41,13 +54,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -194,7 +208,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -229,7 +242,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -264,16 +276,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -395,46 +411,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -445,20 +422,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B163"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.83203125" customWidth="1" min="1" max="1"/>
-    <col width="55.83203125" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Japanese</t>
         </is>
@@ -599,1817 +576,1908 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Weighted</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>はい</t>
+          <t>重み付き</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>On</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>いいえ</t>
+          <t>オン</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中央値</t>
+          <t>オフ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>平均値</t>
+          <t>はい</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>システム</t>
+          <t>いいえ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ライト</t>
+          <t>中央値</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ダーク</t>
+          <t>平均値</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>File Select</t>
+          <t>System</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ファイル選択</t>
+          <t>システム</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Choose char data file</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>データファイルを選択</t>
+          <t>ライト</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Drop files here</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ここにドロップ</t>
+          <t>ダーク</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>or use button above</t>
+          <t>File Select</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>または上のボタンを使用</t>
+          <t>ファイル選択</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sort files alphabetically</t>
+          <t>Choose char data file</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>名前順に並べ替え</t>
+          <t>データファイルを選択</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Drop files here</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>探索</t>
+          <t>ここにドロップ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>or use button above</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>比較</t>
+          <t>または上のボタンを使用</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Display File</t>
+          <t>Sort files alphabetically</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ファイル表示</t>
+          <t>名前順に並べ替え</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Drag files here from</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ここにファイルをドラッグ</t>
+          <t>探索</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>File Select pane or file system</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ファイル選択またはファイルシステムから</t>
+          <t>比較</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3D Plot</t>
+          <t>Display File</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3D プロット</t>
+          <t>ファイル表示</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Drag files here from</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>コントロール</t>
+          <t>ここにファイルをドラッグ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Show gamut shell</t>
+          <t>File Select pane or file system</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ガマットシェルを表示</t>
+          <t>ファイル選択またはファイルシステムから</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Show data points</t>
+          <t>3D Plot</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>データポイントを表示</t>
+          <t>3D プロット</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Color by hue angle</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>色相角で色付け</t>
+          <t>コントロール</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Color by value</t>
+          <t>Show gamut shell</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>明度で色付け</t>
+          <t>ガマットシェルを表示</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Show spectral data when point selected</t>
+          <t>Show data points</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>選択時に分光グラフを表示</t>
+          <t>データポイントを表示</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Computing…</t>
+          <t>Color by hue angle</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>計算中…</t>
+          <t>色相角で色付け</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gamut Slice (2D)</t>
+          <t>Color by value</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ガマットスライス (2D)</t>
+          <t>明度で色付け</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Axis:</t>
+          <t>Show spectral data when point selected</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>軸:</t>
+          <t>選択時に分光グラフを表示</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Value:</t>
+          <t>Computing…</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>値:</t>
+          <t>計算中…</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bandwidth ±</t>
+          <t>Gamut Slice (2D)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>帯域幅 ±</t>
+          <t>ガマットスライス (2D)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>No file loaded</t>
+          <t>Axis:</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ファイル未読み込み</t>
+          <t>軸:</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tone Value</t>
+          <t>Value:</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>トーンバリュー</t>
+          <t>値:</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tone Method</t>
+          <t>No file loaded</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>トーン方法</t>
+          <t>ファイル未読み込み</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Spectral Murray-Davies</t>
+          <t>Tone Value</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>分光 Murray-Davies</t>
+          <t>トーンバリュー</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Colour Tone Value (CTV)</t>
+          <t>Tone Method</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>カラートーンバリュー (CTV)</t>
+          <t>トーン方法</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Spectral Murray-Davies</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>フィルター</t>
+          <t>分光 Murray-Davies</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Graph Type</t>
+          <t>Colour Tone Value (CTV)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>グラフタイプ</t>
+          <t>カラートーンバリュー (CTV)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>トランスファー</t>
+          <t>フィルター</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gain</t>
+          <t>Graph Type</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ゲイン</t>
+          <t>グラフタイプ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>トランスファー</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Datasets</t>
+          <t>Gain</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>データセット</t>
+          <t>ゲイン</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Validate</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>検証</t>
+          <t>理想</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Comparison Table</t>
+          <t>Datasets</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>比較表</t>
+          <t>データセット</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Extract</t>
+          <t>Validate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>抽出</t>
+          <t>検証</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Restore</t>
+          <t>Comparison Table</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>復元</t>
+          <t>比較表</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Extract</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>エクスポート</t>
+          <t>抽出</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Table</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>データ表</t>
+          <t>復元</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>エクスポート</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Primaries</t>
+          <t>Data Table</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>原色</t>
+          <t>データ表</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Secondaries</t>
+          <t>Estimate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>二次色</t>
+          <t>推定</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CMY Grays</t>
+          <t>Primaries</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CMY グレー</t>
+          <t>原色</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CMY Browns</t>
+          <t>Secondaries</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CMY ブラウン</t>
+          <t>二次色</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solids Only</t>
+          <t>CMY Grays</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ソリッドのみ</t>
+          <t>CMY グレー</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Remove paper white point</t>
+          <t>CMY Browns</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>紙白点を除去</t>
+          <t>CMY ブラウン</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Remove selected colorants from data.</t>
+          <t>Solids Only</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>選択した色材をデータから除去します。</t>
+          <t>ソリッドのみ</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Export File</t>
+          <t>Remove paper white point</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ファイルをエクスポート</t>
+          <t>紙白点を除去</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Folder</t>
+          <t>Remove selected colorants from data.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>フォルダー</t>
+          <t>選択した色材をデータから除去します。</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>File name</t>
+          <t>Export File</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ファイル名</t>
+          <t>ファイルをエクスポート</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Folder</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>形式</t>
+          <t>フォルダー</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>File name</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>ファイル名</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>保存</t>
+          <t>形式</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Select folder</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>フォルダーを選択</t>
+          <t>キャンセル</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Browse for folder</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>フォルダーを参照</t>
+          <t>保存</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Folder picker not supported in this browser</t>
+          <t>Select folder</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>このブラウザーはフォルダー選択に対応していません</t>
+          <t>フォルダーを選択</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Export destination folder…</t>
+          <t>Browse for folder</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>エクスポート先フォルダー…</t>
+          <t>フォルダーを参照</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>File is neither CSV nor CGATS/ISO28178 format</t>
+          <t>Folder picker not supported in this browser</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ファイルは CSV でも CGATS/ISO28178 でもありません</t>
+          <t>このブラウザーはフォルダー選択に対応していません</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>✓ Valid</t>
+          <t>File Select: Drop or load files here to select.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>✓ 有効</t>
+          <t>ファイル選択：ここにファイルをドロップまたは読み込み。</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LAB computed from spectral ({ill} / {obs} / {mc})</t>
+          <t>Drag-and-drop files from file system or File Select here</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LAB を分光から算出 ({ill} / {obs} / {mc})</t>
+          <t>ファイルシステムまたはファイル選択からドラッグ＆ドロップ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Missing: {cols}</t>
+          <t>Click to sort</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>不足: {cols}</t>
+          <t>クリックして並び替え</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Loaded {n} rows.</t>
+          <t>Click to view spectral</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{n} 行を読み込みました。</t>
+          <t>クリックしてスペクトル表示</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Loaded {n} rows, reduced to {m} rows by filtering duplicates ({method}).</t>
+          <t>Toggle controls</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{n} 行読み込み、重複フィルター後 {m} 行に削減 ({method})。</t>
+          <t>コントロールの表示切替</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Device colorants:</t>
+          <t>Remove {item}</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>デバイス色材：</t>
+          <t>{item} を削除</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Device colorants: none</t>
+          <t>Click to toggle on/off</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>デバイス色材：なし</t>
+          <t>クリックして切替</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>File contains spectral data. Click on data points to display spectral graph.</t>
+          <t>Export destination folder…</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ファイルに分光データが含まれています。データポイントをクリックすると分光グラフが表示されます。</t>
+          <t>エクスポート先フォルダー…</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Colorimetric only. No spectral data found in file.</t>
+          <t>File is neither CSV nor CGATS/ISO28178 format</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>比色データのみ。ファイルに分光データが見つかりません。</t>
+          <t>ファイルは CSV でも CGATS/ISO28178 でもありません</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>{n} rows (after extract).</t>
+          <t>File header is not standard CGATS (first line does not contain “CGATS” or “ISO28178”)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{n} 行（抽出後）。</t>
+          <t>ファイルヘッダーが標準 CGATS ではありません（1 行目に「CGATS」または「ISO28178」が含まれていません）</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>No comparable inkings between selected files.</t>
+          <t>✓ Valid</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>選択したファイル間に比較可能な色材データがありません。</t>
+          <t>✓ 有効</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>{n} matching data point</t>
+          <t>LAB computed from spectral ({ill} / {obs} / {mc})</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{n} 件の一致データポイント</t>
+          <t>LAB を分光から算出 ({ill} / {obs} / {mc})</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>{n} matching data points</t>
+          <t>Missing: {cols}</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{n} 件の一致データポイント</t>
+          <t>不足: {cols}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mean {method}</t>
+          <t>Loaded {n} rows.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>平均 {method}</t>
+          <t>{n} 行を読み込みました。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Min {method}</t>
+          <t>Loaded {n} rows, reduced to {m} rows by filtering duplicates ({method}).</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>最小 {method}</t>
+          <t>{n} 行読み込み、重複フィルター後 {m} 行に削減 ({method})。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Max {method}</t>
+          <t>Device colorants:</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>最大 {method}</t>
+          <t>デバイス色材：</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Std Dev</t>
+          <t>Device colorants: none</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>標準偏差</t>
+          <t>デバイス色材：なし</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Device Colorants</t>
+          <t>File contains spectral data. Click on data points to display spectral graph.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>デバイス色材</t>
+          <t>ファイルに分光データが含まれています。データポイントをクリックすると分光グラフが表示されます。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Colorimetric only. No spectral data found in file.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>差分</t>
+          <t>比色データのみ。ファイルに分光データが見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Opacity</t>
+          <t>{n} rows (after extract).</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>不透明度</t>
+          <t>{n} 行（抽出後）。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>↻ Regenerate Shell</t>
+          <t>No comparable inkings between selected files.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>↻ シェルを再生成</t>
+          <t>選択したファイル間に比較可能な色材データがありません。</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mesh</t>
+          <t>{n} matching data point</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>メッシュ</t>
+          <t>{n} 件の一致データポイント</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>{n} matching data points</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>密度</t>
+          <t>{n} 件の一致データポイント</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Mean {method}</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>照明</t>
+          <t>平均 {method}</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ambient</t>
+          <t>Min {method}</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>アンビエント</t>
+          <t>最小 {method}</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>diffuse</t>
+          <t>Max {method}</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ディフューズ</t>
+          <t>最大 {method}</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>specular</t>
+          <t>Std Dev</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>スペキュラー</t>
+          <t>標準偏差</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Points fitted</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ラフネス</t>
+          <t>適合点数</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Dataset Settings</t>
+          <t>Dataset {slot}</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>データセット設定</t>
+          <t>データセット {slot}</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Select to toggle file visibility:</t>
+          <t>Device Colorants</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>クリックして表示/非表示：</t>
+          <t>デバイス色材</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Toggle:</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>切替：</t>
+          <t>差分</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Show:</t>
+          <t>Opacity</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>表示：</t>
+          <t>不透明度</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>↻ Regenerate Shell</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>元のファイル</t>
+          <t>↻ シェルを再生成</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Modified</t>
+          <t>Mesh</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>変更済み</t>
+          <t>メッシュ</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>✕ Close</t>
+          <t>Density</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>✕ 閉じる</t>
+          <t>密度</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Selected file is not loaded.</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>選択したファイルが読み込まれていません。</t>
+          <t>照明</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Both files must be loaded.</t>
+          <t>ambient</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>両方のファイルを読み込んでください。</t>
+          <t>アンビエント</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>No K-only patches matched.</t>
+          <t>diffuse</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>K のみのパッチが見つかりません。</t>
+          <t>ディフューズ</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>No CMY patches matched.</t>
+          <t>specular</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CMY パッチが見つかりません。</t>
+          <t>スペキュラー</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Missing CMYK device colorants in Dataset A{name}.</t>
+          <t>roughness</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>データセット A{name} に CMYK デバイス色材がありません。</t>
+          <t>ラフネス</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Missing L*a*b* data in Dataset A{name}.</t>
+          <t>Dataset Settings</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>データセット A{name} に L*a*b* データがありません。</t>
+          <t>データセット設定</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Paper white patch (0,0,0,0) not found in Dataset A.</t>
+          <t>Select to toggle file visibility:</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>データセット A に紙白パッチ (0,0,0,0) が見つかりません。</t>
+          <t>クリックして表示/非表示：</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>100K solid patch not found in Dataset A.</t>
+          <t>Toggle:</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>データセット A に 100K ソリッドパッチが見つかりません。</t>
+          <t>切替：</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>100CMY solid patch not found in Dataset A.</t>
+          <t>Show:</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>データセット A に 100CMY ソリッドパッチが見つかりません。</t>
+          <t>表示：</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>G7 Overall:</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>G7 総合：</t>
+          <t>元のファイル</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Modified</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>スケール</t>
+          <t>変更済み</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tolerance</t>
+          <t>✕ Close</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>許容差</t>
+          <t>✕ 閉じる</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>K (Black)</t>
+          <t>Selected file is not loaded.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>K（ブラック）</t>
+          <t>選択したファイルが読み込まれていません。</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>K patches ({n})</t>
+          <t>Both files must be loaded.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>K パッチ ({n})</t>
+          <t>両方のファイルを読み込んでください。</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CMY patches ({n})</t>
+          <t>No K-only patches matched.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CMY パッチ ({n})</t>
+          <t>K のみのパッチが見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>K%</t>
+          <t>No CMY patches matched.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>K%</t>
+          <t>CMY パッチが見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>L* meas</t>
+          <t>Missing CMYK device colorants in Dataset A{name}.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>L* 測定値</t>
+          <t>データセット A{name} に CMYK デバイス色材がありません。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>L* aim</t>
+          <t>Missing L*a*b* data in Dataset A{name}.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>L* 目標値</t>
+          <t>データセット A{name} に L*a*b* データがありません。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>meas</t>
+          <t>Paper white patch (0,0,0,0) not found in Dataset A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>測定</t>
+          <t>データセット A に紙白パッチ (0,0,0,0) が見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>aim</t>
+          <t>100K solid patch not found in Dataset A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>目標</t>
+          <t>データセット A に 100K ソリッドパッチが見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>No spectral data — switch to Colour Tone Value (CTV)</t>
+          <t>100CMY solid patch not found in Dataset A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>分光データなし — カラートーンバリュー (CTV) に切替</t>
+          <t>データセット A に 100CMY ソリッドパッチが見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>No primary tone steps found.
-Needs rows with a single non-zero colorant.</t>
+          <t>G7 Overall:</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>原色トーンステップが見つかりません。
-単一の非ゼロ色材の行が必要です。</t>
+          <t>G7 総合：</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Tone Value Gain (%)</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>トーンバリューゲイン (%)</t>
+          <t>スケール</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Tone Value (%)</t>
+          <t>Tolerance</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>トーンバリュー (%)</t>
+          <t>許容差</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Input (%)</t>
+          <t>K (Black)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>入力 (%)</t>
+          <t>K（ブラック）</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Model fit — degree {deg}, {n} points</t>
+          <t>K patches ({n})</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>モデル適合 — 次数 {deg}、{n} 点</t>
+          <t>K パッチ ({n})</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>↻ Regenerate</t>
+          <t>CMY patches ({n})</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>↻ 再生成</t>
+          <t>CMY パッチ ({n})</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Input colorant</t>
+          <t>K%</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>入力
-色材</t>
+          <t>K%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Nearest
-in dataset</t>
+          <t>L* meas</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>データセット内
-最近傍</t>
+          <t>L* 測定値</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>L* aim</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>モデル</t>
+          <t>L* 目標値</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Computing…</t>
+          <t>meas</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>計算中…</t>
+          <t>測定</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Model fit failed: {msg}</t>
+          <t>aim</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>モデル適合失敗：{msg}</t>
+          <t>目標</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Retry</t>
+          <t>No spectral data — switch to Colour Tone Value (CTV)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>再試行</t>
+          <t>分光データなし — カラートーンバリュー (CTV) に切替</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Click on L*a*b* color to display spectral graph.</t>
+          <t>No primary tone steps found.\nNeeds rows with a single non-zero colorant.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>L*a*b* カラーをクリックすると分光グラフが表示されます。</t>
+          <t>原色トーンステップが見つかりません。\n単一の非ゼロ色材の行が必要です。</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Scroll to top</t>
+          <t>Tone Value Gain (%)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>トップへ</t>
+          <t>トーンバリューゲイン (%)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Tone Value (%)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ヘルプ</t>
+          <t>トーンバリュー (%)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>About CharData</t>
+          <t>Input (%)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CharData について</t>
+          <t>入力 (%)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Support on Ko-fi</t>
+          <t>Model fit — degree {deg}, {n} points</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ko-fi でサポート</t>
+          <t>モデル適合 — 次数 {deg}、{n} 点</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</t>
+          <t>↻ Regenerate</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CharData はカラーコミュニティのために無料で提供されています。役立つ場合、Ko-fi での少額の寄付が継続に役立ちます。</t>
+          <t>↻ 再生成</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Points fitted</t>
+          <t>Input\ncolorant</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>適合点数</t>
+          <t>入力\n色材</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dataset {slot}</t>
+          <t>Nearest\nin dataset</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>データセット {slot}</t>
+          <t>データセット内\n最近傍</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>File Select: Drop or load files here to select.</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ファイル選択：ここにファイルをドロップまたは読み込み。</t>
+          <t>モデル</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Drag-and-drop files from file system or File Select here</t>
+          <t>Computing…</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ファイルシステムまたはファイル選択からドラッグ＆ドロップ</t>
+          <t>計算中…</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Click to sort</t>
+          <t>Calculating tone values…</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>クリックして並び替え</t>
+          <t>Calculating tone values…</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Click to view spectral</t>
+          <t>Estimating model…</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>クリックしてスペクトル表示</t>
+          <t>Estimating model…</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Toggle controls</t>
+          <t>Building 3D gamut…</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>コントロールの表示切替</t>
+          <t>Building 3D gamut…</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Remove {item}</t>
+          <t>Computing 2D slice…</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>{item} を削除</t>
+          <t>Computing 2D slice…</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Click to toggle on/off</t>
+          <t>Rendering…</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>クリックして切替</t>
+          <t>Rendering…</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Model fit failed: {msg}</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>トップ</t>
+          <t>モデル適合失敗：{msg}</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Buy me a coffee</t>
+          <t>Retry</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>コーヒーをおごってください</t>
+          <t>再試行</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>File header is not standard CGATS (first line does not contain “CGATS” or “ISO28178”)</t>
+          <t>Click on L*a*b* color to display spectral graph.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ファイルヘッダーが標準 CGATS ではありません（1 行目に「CGATS」または「ISO28178」が含まれていません）</t>
+          <t>L*a*b* カラーをクリックすると分光グラフが表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Scroll to top</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>トップへ</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>トップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ヘルプ</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>About CharData</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>CharData について</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Support on Ko-fi</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Ko-fi でサポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Buy me a coffee</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>コーヒーをおごってください</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Reflectance</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>反射率</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CharData はカラーコミュニティのために無料で提供されています。役立つ場合、Ko-fi での少額の寄付が継続に役立ちます。</t>
         </is>
       </c>
     </row>

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B178"/>
+  <dimension ref="A1:B181"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1825,9 +1825,33 @@
         <v>有効な ICC プロファイルではありません（ヘッダーマジックがありません）。</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>Standard datasets</v>
+      </c>
+      <c r="B179" t="str">
+        <v>標準データセット</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>Loading…</v>
+      </c>
+      <c r="B180" t="str">
+        <v>読み込み中…</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Failed to load list</v>
+      </c>
+      <c r="B181" t="str">
+        <v>リストの読み込みに失敗しました</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B178"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -585,12 +585,12 @@
     </row>
     <row r="24" xml:space="preserve">
       <c r="A24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Select files:
-characterization data or ICC profiles</v>
+        <v xml:space="preserve">characterization data
+or ICC profiles</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">ファイルを選択:
-キャラクタリゼーションデータまたは ICC プロファイル</v>
+        <v xml:space="preserve">キャラクタリゼーションデータ
+または ICC プロファイル</v>
       </c>
     </row>
     <row r="25">

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B185"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1849,9 +1849,41 @@
         <v>リストの読み込みに失敗しました</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>Thickness:</v>
+      </c>
+      <c r="B182" t="str">
+        <v>厚さ:</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>Fall-off:</v>
+      </c>
+      <c r="B183" t="str">
+        <v>減衰:</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>Hard</v>
+      </c>
+      <c r="B184" t="str">
+        <v>ハード</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>Soft</v>
+      </c>
+      <c r="B185" t="str">
+        <v>ソフト</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B185"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B189"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1881,9 +1881,41 @@
         <v>ソフト</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>G7 validation is not available for ICC profiles.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>ICC プロファイルでは G7 検証は利用できません。</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>ICC vs ICC comparison requires CMYK profiles.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>ICC 同士の比較には CMYK プロファイルが必要です。</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>Dataset B does not contain colorants matching ICC profile A.</v>
+      </c>
+      <c r="B188" t="str">
+        <v>データセット B には ICC プロファイル A と一致する色材がありません。</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>Dataset A does not contain colorants matching ICC profile B.</v>
+      </c>
+      <c r="B189" t="str">
+        <v>データセット A には ICC プロファイル B と一致する色材がありません。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B185"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B192"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1913,9 +1913,33 @@
         <v>データセット A には ICC プロファイル B と一致する色材がありません。</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Header</v>
+      </c>
+      <c r="B190" t="str">
+        <v>ヘッダー</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Tags</v>
+      </c>
+      <c r="B191" t="str">
+        <v>タグ</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Loading ICC viewer…</v>
+      </c>
+      <c r="B192" t="str">
+        <v>ICC ビューアを読み込み中…</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B192"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B192"/>
+  <dimension ref="A1:B193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1937,9 +1937,17 @@
         <v>ICC ビューアを読み込み中…</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Launch editor</v>
+      </c>
+      <c r="B193" t="str">
+        <v>エディタを開く</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B192"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B193"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1945,9 +1945,25 @@
         <v>エディタを開く</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>All data stays local to browser</v>
+      </c>
+      <c r="B194" t="str">
+        <v>すべてのデータはブラウザー内に保持されます</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Free browser-resident online tool</v>
+      </c>
+      <c r="B195" t="str">
+        <v>ブラウザー上で動作する無料のオンラインツール</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -1561,12 +1561,14 @@
         <v>分光データなし — カラートーンバリュー (CTV) に切替</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>No primary tone steps found.\nNeeds rows with a single non-zero colorant.</v>
-      </c>
-      <c r="B146" t="str">
-        <v>原色トーンステップが見つかりません。\n単一の非ゼロ色材の行が必要です。</v>
+    <row r="146" xml:space="preserve">
+      <c r="A146" t="str" xml:space="preserve">
+        <v xml:space="preserve">No primary tone steps found.
+Needs rows with a single non-zero colorant.</v>
+      </c>
+      <c r="B146" t="str" xml:space="preserve">
+        <v xml:space="preserve">原色トーンステップが見つかりません。
+単一の非ゼロ色材の行が必要です。</v>
       </c>
     </row>
     <row r="147">
@@ -1609,20 +1611,24 @@
         <v>↻ 再生成</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>Input\ncolorant</v>
-      </c>
-      <c r="B152" t="str">
-        <v>入力\n色材</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>Nearest\nin dataset</v>
-      </c>
-      <c r="B153" t="str">
-        <v>データセット内\n最近傍</v>
+    <row r="152" xml:space="preserve">
+      <c r="A152" t="str" xml:space="preserve">
+        <v xml:space="preserve">Input
+colorant</v>
+      </c>
+      <c r="B152" t="str" xml:space="preserve">
+        <v xml:space="preserve">入力
+色材</v>
+      </c>
+    </row>
+    <row r="153" xml:space="preserve">
+      <c r="A153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nearest
+in dataset</v>
+      </c>
+      <c r="B153" t="str" xml:space="preserve">
+        <v xml:space="preserve">データセット内
+最近傍</v>
       </c>
     </row>
     <row r="154">

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B195"/>
+  <dimension ref="A1:B205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1967,9 +1967,89 @@
         <v>ブラウザー上で動作する無料のオンラインツール</v>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Image</v>
+      </c>
+      <c r="B196" t="str">
+        <v>画像</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Load Image</v>
+      </c>
+      <c r="B197" t="str">
+        <v>画像を読み込む</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Bind image to dataset</v>
+      </c>
+      <c r="B198" t="str">
+        <v>画像をデータセットに関連付ける</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Remove image</v>
+      </c>
+      <c r="B199" t="str">
+        <v>画像を削除</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Image color space: {cs} {src}</v>
+      </c>
+      <c r="B200" t="str">
+        <v>画像の色空間：{cs} {src}</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Bound to {name} — {n} points</v>
+      </c>
+      <c r="B201" t="str">
+        <v>{name} に関連付け済み — {n} 点</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Lab image — {n} points</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Lab 画像 — {n} 点</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Cannot bind: image is {img} but Dataset {slot} is {family}.</v>
+      </c>
+      <c r="B203" t="str">
+        <v>関連付けできません：画像は {img} ですが、データセット {slot} は {family} です。</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Unsupported image format. Use PNG, JPEG, or TIFF.</v>
+      </c>
+      <c r="B204" t="str">
+        <v>対応していない画像形式です。PNG、JPEG、または TIFF を使用してください。</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>“{name}” is too large ({mb} MB). Maximum image size is {max} MB.</v>
+      </c>
+      <c r="B205" t="str">
+        <v>「{name}」が大きすぎます（{mb} MB）。最大画像サイズは {max} MB です。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B205"/>
+  <dimension ref="A1:B224"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Unsupported image format. Use PNG, JPEG, or TIFF.</v>
+        <v>Unsupported image format. Use PNG, JPEG, TIFF, BMP, GIF, or PDF.</v>
       </c>
       <c r="B204" t="str">
-        <v>対応していない画像形式です。PNG、JPEG、または TIFF を使用してください。</v>
+        <v>対応していない画像形式です。PNG、JPEG、TIFF、BMP、GIF、または PDF を使用してください。</v>
       </c>
     </row>
     <row r="205">
@@ -2047,9 +2047,161 @@
         <v>「{name}」が大きすぎます（{mb} MB）。最大画像サイズは {max} MB です。</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Embedded: {name}</v>
+      </c>
+      <c r="B206" t="str">
+        <v>埋め込み: {name}</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Decoding image…</v>
+      </c>
+      <c r="B207" t="str">
+        <v>画像をデコード中…</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Image file is too small or corrupt.</v>
+      </c>
+      <c r="B208" t="str">
+        <v>画像ファイルが小さすぎるか破損しています。</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>TIFF decoder library failed to load.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>TIFF デコーダーライブラリの読み込みに失敗しました。</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Selected dataset model is still loading — try again in a moment.</v>
+      </c>
+      <c r="B210" t="str">
+        <v>選択したデータセットのモデルを読み込み中です — 少し待ってから再試行してください。</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Image decode failed.</v>
+      </c>
+      <c r="B211" t="str">
+        <v>画像のデコードに失敗しました。</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Dataset {slot} is not loaded.</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Dataset {slot} は読み込まれていません。</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Embedded profile is no longer available.</v>
+      </c>
+      <c r="B213" t="str">
+        <v>埋め込みプロファイルは利用できなくなりました。</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>(from embedded ICC)</v>
+      </c>
+      <c r="B214" t="str">
+        <v>（埋め込み ICC より）</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>(TIFF Lab)</v>
+      </c>
+      <c r="B215" t="str">
+        <v>（TIFF Lab）</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>(inferred from channels)</v>
+      </c>
+      <c r="B216" t="str">
+        <v>（チャネルから推定）</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>{n} representative points after binning + dedupe</v>
+      </c>
+      <c r="B217" t="str">
+        <v>ビニングと重複除去の後、{n} 個の代表点</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>PDF support is limited to single-image Photoshop PDFs. Save as TIFF, JPEG, PNG, BMP, or GIF for other PDF content.</v>
+      </c>
+      <c r="B218" t="str">
+        <v>PDF のサポートは単一画像の Photoshop PDF に限定されます。他の PDF コンテンツは TIFF、JPEG、PNG、BMP、または GIF として保存してください。</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Encrypted PDFs are not supported.</v>
+      </c>
+      <c r="B219" t="str">
+        <v>暗号化された PDF はサポートされていません。</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Only single-page Photoshop PDFs are supported.</v>
+      </c>
+      <c r="B220" t="str">
+        <v>単一ページの Photoshop PDF のみサポートされます。</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>PDF structure could not be parsed.</v>
+      </c>
+      <c r="B221" t="str">
+        <v>PDF の構造を解析できませんでした。</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>No image found inside the PDF.</v>
+      </c>
+      <c r="B222" t="str">
+        <v>PDF 内に画像が見つかりませんでした。</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>PDF colour space is not supported. Use Gray, RGB, CMYK, or an ICC-based profile.</v>
+      </c>
+      <c r="B223" t="str">
+        <v>PDF の色空間はサポートされていません。グレー、RGB、CMYK、または ICC ベースのプロファイルを使用してください。</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>PDF image filter is not supported. Re-save the PDF with JPEG or ZIP compression.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>PDF の画像フィルターはサポートされていません。JPEG または ZIP 圧縮で PDF を保存し直してください。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B224"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B224"/>
+  <dimension ref="A1:B242"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2199,9 +2199,153 @@
         <v>PDF の画像フィルターはサポートされていません。JPEG または ZIP 圧縮で PDF を保存し直してください。</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close file select</v>
+      </c>
+      <c r="B225" t="str">
+        <v>ファイル選択を閉じる</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Drag to resize</v>
+      </c>
+      <c r="B226" t="str">
+        <v>ドラッグしてサイズ変更</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Contact</v>
+      </c>
+      <c r="B227" t="str">
+        <v>お問い合わせ</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>Remove file</v>
+      </c>
+      <c r="B228" t="str">
+        <v>ファイルを削除</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>Rendering intent:</v>
+      </c>
+      <c r="B229" t="str">
+        <v>レンダリングインテント：</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>Perceptual</v>
+      </c>
+      <c r="B230" t="str">
+        <v>知覚的</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>Relative Colorimetric</v>
+      </c>
+      <c r="B231" t="str">
+        <v>相対比色</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Saturation</v>
+      </c>
+      <c r="B232" t="str">
+        <v>彩度</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Absolute Colorimetric</v>
+      </c>
+      <c r="B233" t="str">
+        <v>絶対比色</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>System default ({lang})</v>
+      </c>
+      <c r="B234" t="str">
+        <v>システム既定（{lang}）</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>ICC load error: {msg}</v>
+      </c>
+      <c r="B235" t="str">
+        <v>ICC 読み込みエラー：{msg}</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>Could not parse ICC profile: {msg}</v>
+      </c>
+      <c r="B236" t="str">
+        <v>ICC プロファイルを解析できませんでした：{msg}</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Popup blocked — allow popups for this site to launch the editor.</v>
+      </c>
+      <c r="B237" t="str">
+        <v>ポップアップがブロックされました — エディターを起動するにはこのサイトのポップアップを許可してください。</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Failed to load {name}: {msg}</v>
+      </c>
+      <c r="B238" t="str">
+        <v>{name} の読み込みに失敗しました：{msg}</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Color space</v>
+      </c>
+      <c r="B239" t="str">
+        <v>色空間</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Device class</v>
+      </c>
+      <c r="B240" t="str">
+        <v>デバイスクラス</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Colorants</v>
+      </c>
+      <c r="B241" t="str">
+        <v>色材</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>Rendering intents</v>
+      </c>
+      <c r="B242" t="str">
+        <v>レンダリングインテント</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B242"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B244"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2343,9 +2343,25 @@
         <v>レンダリングインテント</v>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>ICC A2B Evaluation</v>
+      </c>
+      <c r="B243" t="str">
+        <v>ICC A2B 評価</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>ICC Output</v>
+      </c>
+      <c r="B244" t="str">
+        <v>ICC 出力</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B242"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B244"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B244"/>
+  <dimension ref="A1:B248"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2359,9 +2359,41 @@
         <v>ICC 出力</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>Image detail</v>
+      </c>
+      <c r="B245" t="str">
+        <v>画像の精度</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>Coarse</v>
+      </c>
+      <c r="B246" t="str">
+        <v>粗い</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="B247" t="str">
+        <v>標準</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>Fine</v>
+      </c>
+      <c r="B248" t="str">
+        <v>細かい</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B244"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B248"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B248"/>
+  <dimension ref="A1:B263"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2391,9 +2391,129 @@
         <v>細かい</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B249" t="str">
+        <v>通知を受け取る</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Get notified about new chardata releases</v>
+      </c>
+      <c r="B250" t="str">
+        <v>chardataの新リリース通知を受け取る</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B251" t="str">
+        <v>新しいリリースの通知を受け取る</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B252" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>We’ll email you when a new major or minor chardata release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B253" t="str">
+        <v>chardataのメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B254" t="str">
+        <v>メールアドレス</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B255" t="str">
+        <v>you@example.com</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>How will you use chardata?</v>
+      </c>
+      <c r="B256" t="str">
+        <v>chardataをどのように使いますか？</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B257" t="str">
+        <v>（任意）</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B258" t="str">
+        <v>例：印刷校正のためのICCプロファイル評価</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>I agree to receive emails about chardata releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>chardataのリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B260" t="str">
+        <v>登録</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B261" t="str">
+        <v>ありがとうございます — ご連絡します。</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new chardata release ships.</v>
+      </c>
+      <c r="B262" t="str">
+        <v>承認後、ウェルカムメールをお送りします。その後はchardataの新リリース時のみご連絡します。</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B263" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B248"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B263"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B264"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2511,9 +2511,17 @@
         <v>閉じる</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B264" t="str">
+        <v>プライバシーに関する通知</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B263"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B264"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Dataset {slot} is not loaded.</v>
+        <v>No color dataset loaded.</v>
       </c>
       <c r="B212" t="str">
-        <v>Dataset {slot} は読み込まれていません。</v>
+        <v>カラーデータセットが読み込まれていません。</v>
       </c>
     </row>
     <row r="213">

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -1897,10 +1897,10 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ICC vs ICC comparison requires CMYK profiles.</v>
+        <v>ICC vs ICC comparison requires identical colorant lists. Profile A: {a}. Profile B: {b}.</v>
       </c>
       <c r="B187" t="str">
-        <v>ICC 同士の比較には CMYK プロファイルが必要です。</v>
+        <v>ICC 同士の比較には同一の色材リストが必要です。プロファイル A: {a}。プロファイル B: {b}。</v>
       </c>
     </row>
     <row r="188">

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B269"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2519,9 +2519,49 @@
         <v>プライバシーに関する通知</v>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Measurement-only data (no device colorants): 3D and 2D-slice point cloud, data table, and label-matched compare are available; gamut shell, extract, tone value, estimate, and validation are disabled.</v>
+      </c>
+      <c r="B265" t="str">
+        <v>測定データのみ（デバイス色材なし）：3D および 2D スライスの点群、データ表、ラベル一致比較が利用可能。ガマットシェル、抽出、トーンバリュー、推定、検証は無効です。</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Sample</v>
+      </c>
+      <c r="B266" t="str">
+        <v>サンプル</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>CxF file is not well-formed XML.</v>
+      </c>
+      <c r="B267" t="str">
+        <v>CxF ファイルが整形式 XML ではありません。</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>CxF file contains no colour objects.</v>
+      </c>
+      <c r="B268" t="str">
+        <v>CxF ファイルにカラーオブジェクトが含まれていません。</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>CxF file contains no CIELab or spectral colour values.</v>
+      </c>
+      <c r="B269" t="str">
+        <v>CxF ファイルに CIELab または分光カラー値が含まれていません。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B264"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B269"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B269"/>
+  <dimension ref="A1:B268"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1275,1293 +1275,1285 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>↻ Regenerate Shell</v>
+        <v>Mesh</v>
       </c>
       <c r="B110" t="str">
-        <v>↻ シェルを再生成</v>
+        <v>メッシュ</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Mesh</v>
+        <v>Density</v>
       </c>
       <c r="B111" t="str">
-        <v>メッシュ</v>
+        <v>密度</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Density</v>
+        <v>Lighting</v>
       </c>
       <c r="B112" t="str">
-        <v>密度</v>
+        <v>照明</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Lighting</v>
+        <v>ambient</v>
       </c>
       <c r="B113" t="str">
-        <v>照明</v>
+        <v>アンビエント</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ambient</v>
+        <v>diffuse</v>
       </c>
       <c r="B114" t="str">
-        <v>アンビエント</v>
+        <v>ディフューズ</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>diffuse</v>
+        <v>specular</v>
       </c>
       <c r="B115" t="str">
-        <v>ディフューズ</v>
+        <v>スペキュラー</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>specular</v>
+        <v>roughness</v>
       </c>
       <c r="B116" t="str">
-        <v>スペキュラー</v>
+        <v>ラフネス</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>roughness</v>
+        <v>Dataset Settings</v>
       </c>
       <c r="B117" t="str">
-        <v>ラフネス</v>
+        <v>データセット設定</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Dataset Settings</v>
+        <v>Select to toggle file visibility:</v>
       </c>
       <c r="B118" t="str">
-        <v>データセット設定</v>
+        <v>クリックして表示/非表示：</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Select to toggle file visibility:</v>
+        <v>Toggle:</v>
       </c>
       <c r="B119" t="str">
-        <v>クリックして表示/非表示：</v>
+        <v>切替：</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Toggle:</v>
+        <v>Show:</v>
       </c>
       <c r="B120" t="str">
-        <v>切替：</v>
+        <v>表示：</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Show:</v>
+        <v>Original</v>
       </c>
       <c r="B121" t="str">
-        <v>表示：</v>
+        <v>元のファイル</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Original</v>
+        <v>Modified</v>
       </c>
       <c r="B122" t="str">
-        <v>元のファイル</v>
+        <v>変更済み</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Modified</v>
+        <v>✕ Close</v>
       </c>
       <c r="B123" t="str">
-        <v>変更済み</v>
+        <v>✕ 閉じる</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>✕ Close</v>
+        <v>Selected file is not loaded.</v>
       </c>
       <c r="B124" t="str">
-        <v>✕ 閉じる</v>
+        <v>選択したファイルが読み込まれていません。</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Selected file is not loaded.</v>
+        <v>Both files must be loaded.</v>
       </c>
       <c r="B125" t="str">
-        <v>選択したファイルが読み込まれていません。</v>
+        <v>両方のファイルを読み込んでください。</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Both files must be loaded.</v>
+        <v>No K-only patches matched.</v>
       </c>
       <c r="B126" t="str">
-        <v>両方のファイルを読み込んでください。</v>
+        <v>K のみのパッチが見つかりません。</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>No K-only patches matched.</v>
+        <v>No CMY patches matched.</v>
       </c>
       <c r="B127" t="str">
-        <v>K のみのパッチが見つかりません。</v>
+        <v>CMY パッチが見つかりません。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>No CMY patches matched.</v>
+        <v>Missing CMYK device colorants in Dataset A{name}.</v>
       </c>
       <c r="B128" t="str">
-        <v>CMY パッチが見つかりません。</v>
+        <v>データセット A{name} に CMYK デバイス色材がありません。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Missing CMYK device colorants in Dataset A{name}.</v>
+        <v>Missing L*a*b* data in Dataset A{name}.</v>
       </c>
       <c r="B129" t="str">
-        <v>データセット A{name} に CMYK デバイス色材がありません。</v>
+        <v>データセット A{name} に L*a*b* データがありません。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Missing L*a*b* data in Dataset A{name}.</v>
+        <v>Paper white patch (0,0,0,0) not found in Dataset A.</v>
       </c>
       <c r="B130" t="str">
-        <v>データセット A{name} に L*a*b* データがありません。</v>
+        <v>データセット A に紙白パッチ (0,0,0,0) が見つかりません。</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Paper white patch (0,0,0,0) not found in Dataset A.</v>
+        <v>100K solid patch not found in Dataset A.</v>
       </c>
       <c r="B131" t="str">
-        <v>データセット A に紙白パッチ (0,0,0,0) が見つかりません。</v>
+        <v>データセット A に 100K ソリッドパッチが見つかりません。</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>100K solid patch not found in Dataset A.</v>
+        <v>100CMY solid patch not found in Dataset A.</v>
       </c>
       <c r="B132" t="str">
-        <v>データセット A に 100K ソリッドパッチが見つかりません。</v>
+        <v>データセット A に 100CMY ソリッドパッチが見つかりません。</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>100CMY solid patch not found in Dataset A.</v>
+        <v>G7 Overall:</v>
       </c>
       <c r="B133" t="str">
-        <v>データセット A に 100CMY ソリッドパッチが見つかりません。</v>
+        <v>G7 総合：</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>G7 Overall:</v>
+        <v>Scale</v>
       </c>
       <c r="B134" t="str">
-        <v>G7 総合：</v>
+        <v>スケール</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Scale</v>
+        <v>Tolerance</v>
       </c>
       <c r="B135" t="str">
-        <v>スケール</v>
+        <v>許容差</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Tolerance</v>
+        <v>K (Black)</v>
       </c>
       <c r="B136" t="str">
-        <v>許容差</v>
+        <v>K（ブラック）</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>K (Black)</v>
+        <v>K patches ({n})</v>
       </c>
       <c r="B137" t="str">
-        <v>K（ブラック）</v>
+        <v>K パッチ ({n})</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>K patches ({n})</v>
+        <v>CMY patches ({n})</v>
       </c>
       <c r="B138" t="str">
-        <v>K パッチ ({n})</v>
+        <v>CMY パッチ ({n})</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>CMY patches ({n})</v>
+        <v>K%</v>
       </c>
       <c r="B139" t="str">
-        <v>CMY パッチ ({n})</v>
+        <v>K%</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>K%</v>
+        <v>L* meas</v>
       </c>
       <c r="B140" t="str">
-        <v>K%</v>
+        <v>L* 測定値</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>L* meas</v>
+        <v>L* aim</v>
       </c>
       <c r="B141" t="str">
-        <v>L* 測定値</v>
+        <v>L* 目標値</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L* aim</v>
+        <v>meas</v>
       </c>
       <c r="B142" t="str">
-        <v>L* 目標値</v>
+        <v>測定</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>meas</v>
+        <v>aim</v>
       </c>
       <c r="B143" t="str">
-        <v>測定</v>
+        <v>目標</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>aim</v>
+        <v>No spectral data — switch to Colour Tone Value (CTV)</v>
       </c>
       <c r="B144" t="str">
-        <v>目標</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>No spectral data — switch to Colour Tone Value (CTV)</v>
-      </c>
-      <c r="B145" t="str">
         <v>分光データなし — カラートーンバリュー (CTV) に切替</v>
       </c>
     </row>
-    <row r="146" xml:space="preserve">
-      <c r="A146" t="str" xml:space="preserve">
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str" xml:space="preserve">
         <v xml:space="preserve">No primary tone steps found.
 Needs rows with a single non-zero colorant.</v>
       </c>
-      <c r="B146" t="str" xml:space="preserve">
+      <c r="B145" t="str" xml:space="preserve">
         <v xml:space="preserve">原色トーンステップが見つかりません。
 単一の非ゼロ色材の行が必要です。</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tone Value Gain (%)</v>
+      </c>
+      <c r="B146" t="str">
+        <v>トーンバリューゲイン (%)</v>
+      </c>
+    </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Tone Value Gain (%)</v>
+        <v>Tone Value (%)</v>
       </c>
       <c r="B147" t="str">
-        <v>トーンバリューゲイン (%)</v>
+        <v>トーンバリュー (%)</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Tone Value (%)</v>
+        <v>Input (%)</v>
       </c>
       <c r="B148" t="str">
-        <v>トーンバリュー (%)</v>
+        <v>入力 (%)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Input (%)</v>
+        <v>Model fit — degree {deg}, {n} points</v>
       </c>
       <c r="B149" t="str">
-        <v>入力 (%)</v>
+        <v>モデル適合 — 次数 {deg}、{n} 点</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Model fit — degree {deg}, {n} points</v>
+        <v>↻ Regenerate</v>
       </c>
       <c r="B150" t="str">
-        <v>モデル適合 — 次数 {deg}、{n} 点</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>↻ Regenerate</v>
-      </c>
-      <c r="B151" t="str">
         <v>↻ 再生成</v>
+      </c>
+    </row>
+    <row r="151" xml:space="preserve">
+      <c r="A151" t="str" xml:space="preserve">
+        <v xml:space="preserve">Input
+colorant</v>
+      </c>
+      <c r="B151" t="str" xml:space="preserve">
+        <v xml:space="preserve">入力
+色材</v>
       </c>
     </row>
     <row r="152" xml:space="preserve">
       <c r="A152" t="str" xml:space="preserve">
-        <v xml:space="preserve">Input
-colorant</v>
-      </c>
-      <c r="B152" t="str" xml:space="preserve">
-        <v xml:space="preserve">入力
-色材</v>
-      </c>
-    </row>
-    <row r="153" xml:space="preserve">
-      <c r="A153" t="str" xml:space="preserve">
         <v xml:space="preserve">Nearest
 in dataset</v>
       </c>
-      <c r="B153" t="str" xml:space="preserve">
+      <c r="B152" t="str" xml:space="preserve">
         <v xml:space="preserve">データセット内
 最近傍</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Model</v>
+      </c>
+      <c r="B153" t="str">
+        <v>モデル</v>
+      </c>
+    </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Model</v>
+        <v>Computing…</v>
       </c>
       <c r="B154" t="str">
-        <v>モデル</v>
+        <v>計算中…</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Computing…</v>
+        <v>Calculating tone values…</v>
       </c>
       <c r="B155" t="str">
-        <v>計算中…</v>
+        <v>Calculating tone values…</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Calculating tone values…</v>
+        <v>Estimating model…</v>
       </c>
       <c r="B156" t="str">
-        <v>Calculating tone values…</v>
+        <v>Estimating model…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Estimating model…</v>
+        <v>Building 3D gamut…</v>
       </c>
       <c r="B157" t="str">
-        <v>Estimating model…</v>
+        <v>Building 3D gamut…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Building 3D gamut…</v>
+        <v>Computing 2D slice…</v>
       </c>
       <c r="B158" t="str">
-        <v>Building 3D gamut…</v>
+        <v>Computing 2D slice…</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Computing 2D slice…</v>
+        <v>Rendering…</v>
       </c>
       <c r="B159" t="str">
-        <v>Computing 2D slice…</v>
+        <v>Rendering…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Rendering…</v>
+        <v>Model fit failed: {msg}</v>
       </c>
       <c r="B160" t="str">
-        <v>Rendering…</v>
+        <v>モデル適合失敗：{msg}</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Model fit failed: {msg}</v>
+        <v>Retry</v>
       </c>
       <c r="B161" t="str">
-        <v>モデル適合失敗：{msg}</v>
+        <v>再試行</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Retry</v>
+        <v>Click on L*a*b* color to display spectral graph.</v>
       </c>
       <c r="B162" t="str">
-        <v>再試行</v>
+        <v>L*a*b* カラーをクリックすると分光グラフが表示されます。</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Click on L*a*b* color to display spectral graph.</v>
+        <v>Scroll to top</v>
       </c>
       <c r="B163" t="str">
-        <v>L*a*b* カラーをクリックすると分光グラフが表示されます。</v>
+        <v>トップへ</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Scroll to top</v>
+        <v>Top</v>
       </c>
       <c r="B164" t="str">
-        <v>トップへ</v>
+        <v>トップ</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Top</v>
+        <v>Help</v>
       </c>
       <c r="B165" t="str">
-        <v>トップ</v>
+        <v>ヘルプ</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Help</v>
+        <v>About CharData</v>
       </c>
       <c r="B166" t="str">
-        <v>ヘルプ</v>
+        <v>CharData について</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>About CharData</v>
+        <v>Support on Ko-fi</v>
       </c>
       <c r="B167" t="str">
-        <v>CharData について</v>
+        <v>Ko-fi でサポート</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Support on Ko-fi</v>
+        <v>Buy me a coffee</v>
       </c>
       <c r="B168" t="str">
-        <v>Ko-fi でサポート</v>
+        <v>コーヒーをおごってください</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Buy me a coffee</v>
+        <v>Reflectance</v>
       </c>
       <c r="B169" t="str">
-        <v>コーヒーをおごってください</v>
+        <v>反射率</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Reflectance</v>
+        <v>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</v>
       </c>
       <c r="B170" t="str">
-        <v>反射率</v>
+        <v>CharData はカラーコミュニティのために無料で提供されています。役立つ場合、Ko-fi での少額の寄付が継続に役立ちます。</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</v>
+        <v>Characterization data</v>
       </c>
       <c r="B171" t="str">
-        <v>CharData はカラーコミュニティのために無料で提供されています。役立つ場合、Ko-fi での少額の寄付が継続に役立ちます。</v>
+        <v>キャラクタリゼーションデータ</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Characterization data</v>
+        <v>ICC Profiles</v>
       </c>
       <c r="B172" t="str">
-        <v>キャラクタリゼーションデータ</v>
+        <v>ICC プロファイル</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>ICC Profiles</v>
+        <v>No characterization datasets loaded</v>
       </c>
       <c r="B173" t="str">
-        <v>ICC プロファイル</v>
+        <v>キャラクタリゼーションデータが読み込まれていません</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>No characterization datasets loaded</v>
+        <v>No ICC profiles loaded</v>
       </c>
       <c r="B174" t="str">
-        <v>キャラクタリゼーションデータが読み込まれていません</v>
+        <v>ICC プロファイルが読み込まれていません</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>No ICC profiles loaded</v>
+        <v>Characterization dataset</v>
       </c>
       <c r="B175" t="str">
-        <v>ICC プロファイルが読み込まれていません</v>
+        <v>キャラクタリゼーションデータ</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Characterization dataset</v>
+        <v>ICC Profile</v>
       </c>
       <c r="B176" t="str">
-        <v>キャラクタリゼーションデータ</v>
+        <v>ICC プロファイル</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>ICC Profile</v>
+        <v>Not a valid ICC profile (header magic missing).</v>
       </c>
       <c r="B177" t="str">
-        <v>ICC プロファイル</v>
+        <v>有効な ICC プロファイルではありません（ヘッダーマジックがありません）。</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Not a valid ICC profile (header magic missing).</v>
+        <v>Standard datasets</v>
       </c>
       <c r="B178" t="str">
-        <v>有効な ICC プロファイルではありません（ヘッダーマジックがありません）。</v>
+        <v>標準データセット</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Standard datasets</v>
+        <v>Loading…</v>
       </c>
       <c r="B179" t="str">
-        <v>標準データセット</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading…</v>
+        <v>Failed to load list</v>
       </c>
       <c r="B180" t="str">
-        <v>読み込み中…</v>
+        <v>リストの読み込みに失敗しました</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Failed to load list</v>
+        <v>Thickness:</v>
       </c>
       <c r="B181" t="str">
-        <v>リストの読み込みに失敗しました</v>
+        <v>厚さ:</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Thickness:</v>
+        <v>Fall-off:</v>
       </c>
       <c r="B182" t="str">
-        <v>厚さ:</v>
+        <v>減衰:</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fall-off:</v>
+        <v>Hard</v>
       </c>
       <c r="B183" t="str">
-        <v>減衰:</v>
+        <v>ハード</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Hard</v>
+        <v>Soft</v>
       </c>
       <c r="B184" t="str">
-        <v>ハード</v>
+        <v>ソフト</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Soft</v>
+        <v>G7 validation is not available for ICC profiles.</v>
       </c>
       <c r="B185" t="str">
-        <v>ソフト</v>
+        <v>ICC プロファイルでは G7 検証は利用できません。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>G7 validation is not available for ICC profiles.</v>
+        <v>ICC vs ICC comparison requires identical colorant lists. Profile A: {a}. Profile B: {b}.</v>
       </c>
       <c r="B186" t="str">
-        <v>ICC プロファイルでは G7 検証は利用できません。</v>
+        <v>ICC 同士の比較には同一の色材リストが必要です。プロファイル A: {a}。プロファイル B: {b}。</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ICC vs ICC comparison requires identical colorant lists. Profile A: {a}. Profile B: {b}.</v>
+        <v>Dataset B does not contain colorants matching ICC profile A.</v>
       </c>
       <c r="B187" t="str">
-        <v>ICC 同士の比較には同一の色材リストが必要です。プロファイル A: {a}。プロファイル B: {b}。</v>
+        <v>データセット B には ICC プロファイル A と一致する色材がありません。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Dataset B does not contain colorants matching ICC profile A.</v>
+        <v>Dataset A does not contain colorants matching ICC profile B.</v>
       </c>
       <c r="B188" t="str">
-        <v>データセット B には ICC プロファイル A と一致する色材がありません。</v>
+        <v>データセット A には ICC プロファイル B と一致する色材がありません。</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Dataset A does not contain colorants matching ICC profile B.</v>
+        <v>Header</v>
       </c>
       <c r="B189" t="str">
-        <v>データセット A には ICC プロファイル B と一致する色材がありません。</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Header</v>
+        <v>Tags</v>
       </c>
       <c r="B190" t="str">
-        <v>ヘッダー</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Tags</v>
+        <v>Loading ICC viewer…</v>
       </c>
       <c r="B191" t="str">
-        <v>タグ</v>
+        <v>ICC ビューアを読み込み中…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Loading ICC viewer…</v>
+        <v>Launch editor</v>
       </c>
       <c r="B192" t="str">
-        <v>ICC ビューアを読み込み中…</v>
+        <v>エディタを開く</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Launch editor</v>
+        <v>All data stays local to browser</v>
       </c>
       <c r="B193" t="str">
-        <v>エディタを開く</v>
+        <v>すべてのデータはブラウザー内に保持されます</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>All data stays local to browser</v>
+        <v>Free browser-resident online tool</v>
       </c>
       <c r="B194" t="str">
-        <v>すべてのデータはブラウザー内に保持されます</v>
+        <v>ブラウザー上で動作する無料のオンラインツール</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Free browser-resident online tool</v>
+        <v>Image</v>
       </c>
       <c r="B195" t="str">
-        <v>ブラウザー上で動作する無料のオンラインツール</v>
+        <v>画像</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Image</v>
+        <v>Load Image</v>
       </c>
       <c r="B196" t="str">
-        <v>画像</v>
+        <v>画像を読み込む</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Load Image</v>
+        <v>Bind image to dataset</v>
       </c>
       <c r="B197" t="str">
-        <v>画像を読み込む</v>
+        <v>画像をデータセットに関連付ける</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Bind image to dataset</v>
+        <v>Remove image</v>
       </c>
       <c r="B198" t="str">
-        <v>画像をデータセットに関連付ける</v>
+        <v>画像を削除</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Remove image</v>
+        <v>Image color space: {cs} {src}</v>
       </c>
       <c r="B199" t="str">
-        <v>画像を削除</v>
+        <v>画像の色空間：{cs} {src}</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Image color space: {cs} {src}</v>
+        <v>Bound to {name} — {n} points</v>
       </c>
       <c r="B200" t="str">
-        <v>画像の色空間：{cs} {src}</v>
+        <v>{name} に関連付け済み — {n} 点</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Bound to {name} — {n} points</v>
+        <v>Lab image — {n} points</v>
       </c>
       <c r="B201" t="str">
-        <v>{name} に関連付け済み — {n} 点</v>
+        <v>Lab 画像 — {n} 点</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Lab image — {n} points</v>
+        <v>Cannot bind: image is {img} but Dataset {slot} is {family}.</v>
       </c>
       <c r="B202" t="str">
-        <v>Lab 画像 — {n} 点</v>
+        <v>関連付けできません：画像は {img} ですが、データセット {slot} は {family} です。</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Cannot bind: image is {img} but Dataset {slot} is {family}.</v>
+        <v>Unsupported image format. Use PNG, JPEG, TIFF, BMP, GIF, or PDF.</v>
       </c>
       <c r="B203" t="str">
-        <v>関連付けできません：画像は {img} ですが、データセット {slot} は {family} です。</v>
+        <v>対応していない画像形式です。PNG、JPEG、TIFF、BMP、GIF、または PDF を使用してください。</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Unsupported image format. Use PNG, JPEG, TIFF, BMP, GIF, or PDF.</v>
+        <v>“{name}” is too large ({mb} MB). Maximum image size is {max} MB.</v>
       </c>
       <c r="B204" t="str">
-        <v>対応していない画像形式です。PNG、JPEG、TIFF、BMP、GIF、または PDF を使用してください。</v>
+        <v>「{name}」が大きすぎます（{mb} MB）。最大画像サイズは {max} MB です。</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>“{name}” is too large ({mb} MB). Maximum image size is {max} MB.</v>
+        <v>Embedded: {name}</v>
       </c>
       <c r="B205" t="str">
-        <v>「{name}」が大きすぎます（{mb} MB）。最大画像サイズは {max} MB です。</v>
+        <v>埋め込み: {name}</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Embedded: {name}</v>
+        <v>Decoding image…</v>
       </c>
       <c r="B206" t="str">
-        <v>埋め込み: {name}</v>
+        <v>画像をデコード中…</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Decoding image…</v>
+        <v>Image file is too small or corrupt.</v>
       </c>
       <c r="B207" t="str">
-        <v>画像をデコード中…</v>
+        <v>画像ファイルが小さすぎるか破損しています。</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Image file is too small or corrupt.</v>
+        <v>TIFF decoder library failed to load.</v>
       </c>
       <c r="B208" t="str">
-        <v>画像ファイルが小さすぎるか破損しています。</v>
+        <v>TIFF デコーダーライブラリの読み込みに失敗しました。</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>TIFF decoder library failed to load.</v>
+        <v>Selected dataset model is still loading — try again in a moment.</v>
       </c>
       <c r="B209" t="str">
-        <v>TIFF デコーダーライブラリの読み込みに失敗しました。</v>
+        <v>選択したデータセットのモデルを読み込み中です — 少し待ってから再試行してください。</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Selected dataset model is still loading — try again in a moment.</v>
+        <v>Image decode failed.</v>
       </c>
       <c r="B210" t="str">
-        <v>選択したデータセットのモデルを読み込み中です — 少し待ってから再試行してください。</v>
+        <v>画像のデコードに失敗しました。</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Image decode failed.</v>
+        <v>No color dataset loaded.</v>
       </c>
       <c r="B211" t="str">
-        <v>画像のデコードに失敗しました。</v>
+        <v>カラーデータセットが読み込まれていません。</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>No color dataset loaded.</v>
+        <v>Embedded profile is no longer available.</v>
       </c>
       <c r="B212" t="str">
-        <v>カラーデータセットが読み込まれていません。</v>
+        <v>埋め込みプロファイルは利用できなくなりました。</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Embedded profile is no longer available.</v>
+        <v>(from embedded ICC)</v>
       </c>
       <c r="B213" t="str">
-        <v>埋め込みプロファイルは利用できなくなりました。</v>
+        <v>（埋め込み ICC より）</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>(from embedded ICC)</v>
+        <v>(TIFF Lab)</v>
       </c>
       <c r="B214" t="str">
-        <v>（埋め込み ICC より）</v>
+        <v>（TIFF Lab）</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>(TIFF Lab)</v>
+        <v>(inferred from channels)</v>
       </c>
       <c r="B215" t="str">
-        <v>（TIFF Lab）</v>
+        <v>（チャネルから推定）</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>(inferred from channels)</v>
+        <v>{n} representative points after binning + dedupe</v>
       </c>
       <c r="B216" t="str">
-        <v>（チャネルから推定）</v>
+        <v>ビニングと重複除去の後、{n} 個の代表点</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>{n} representative points after binning + dedupe</v>
+        <v>PDF support is limited to single-image Photoshop PDFs. Save as TIFF, JPEG, PNG, BMP, or GIF for other PDF content.</v>
       </c>
       <c r="B217" t="str">
-        <v>ビニングと重複除去の後、{n} 個の代表点</v>
+        <v>PDF のサポートは単一画像の Photoshop PDF に限定されます。他の PDF コンテンツは TIFF、JPEG、PNG、BMP、または GIF として保存してください。</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PDF support is limited to single-image Photoshop PDFs. Save as TIFF, JPEG, PNG, BMP, or GIF for other PDF content.</v>
+        <v>Encrypted PDFs are not supported.</v>
       </c>
       <c r="B218" t="str">
-        <v>PDF のサポートは単一画像の Photoshop PDF に限定されます。他の PDF コンテンツは TIFF、JPEG、PNG、BMP、または GIF として保存してください。</v>
+        <v>暗号化された PDF はサポートされていません。</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Encrypted PDFs are not supported.</v>
+        <v>Only single-page Photoshop PDFs are supported.</v>
       </c>
       <c r="B219" t="str">
-        <v>暗号化された PDF はサポートされていません。</v>
+        <v>単一ページの Photoshop PDF のみサポートされます。</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Only single-page Photoshop PDFs are supported.</v>
+        <v>PDF structure could not be parsed.</v>
       </c>
       <c r="B220" t="str">
-        <v>単一ページの Photoshop PDF のみサポートされます。</v>
+        <v>PDF の構造を解析できませんでした。</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>PDF structure could not be parsed.</v>
+        <v>No image found inside the PDF.</v>
       </c>
       <c r="B221" t="str">
-        <v>PDF の構造を解析できませんでした。</v>
+        <v>PDF 内に画像が見つかりませんでした。</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>No image found inside the PDF.</v>
+        <v>PDF colour space is not supported. Use Gray, RGB, CMYK, or an ICC-based profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>PDF 内に画像が見つかりませんでした。</v>
+        <v>PDF の色空間はサポートされていません。グレー、RGB、CMYK、または ICC ベースのプロファイルを使用してください。</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>PDF colour space is not supported. Use Gray, RGB, CMYK, or an ICC-based profile.</v>
+        <v>PDF image filter is not supported. Re-save the PDF with JPEG or ZIP compression.</v>
       </c>
       <c r="B223" t="str">
-        <v>PDF の色空間はサポートされていません。グレー、RGB、CMYK、または ICC ベースのプロファイルを使用してください。</v>
+        <v>PDF の画像フィルターはサポートされていません。JPEG または ZIP 圧縮で PDF を保存し直してください。</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>PDF image filter is not supported. Re-save the PDF with JPEG or ZIP compression.</v>
+        <v>Close file select</v>
       </c>
       <c r="B224" t="str">
-        <v>PDF の画像フィルターはサポートされていません。JPEG または ZIP 圧縮で PDF を保存し直してください。</v>
+        <v>ファイル選択を閉じる</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close file select</v>
+        <v>Drag to resize</v>
       </c>
       <c r="B225" t="str">
-        <v>ファイル選択を閉じる</v>
+        <v>ドラッグしてサイズ変更</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Drag to resize</v>
+        <v>Contact</v>
       </c>
       <c r="B226" t="str">
-        <v>ドラッグしてサイズ変更</v>
+        <v>お問い合わせ</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Contact</v>
+        <v>Remove file</v>
       </c>
       <c r="B227" t="str">
-        <v>お問い合わせ</v>
+        <v>ファイルを削除</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Remove file</v>
+        <v>Rendering intent:</v>
       </c>
       <c r="B228" t="str">
-        <v>ファイルを削除</v>
+        <v>レンダリングインテント：</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Rendering intent:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B229" t="str">
-        <v>レンダリングインテント：</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Perceptual</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B230" t="str">
-        <v>知覚的</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B231" t="str">
-        <v>相対比色</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Saturation</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B232" t="str">
-        <v>彩度</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>System default ({lang})</v>
       </c>
       <c r="B233" t="str">
-        <v>絶対比色</v>
+        <v>システム既定（{lang}）</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>System default ({lang})</v>
+        <v>ICC load error: {msg}</v>
       </c>
       <c r="B234" t="str">
-        <v>システム既定（{lang}）</v>
+        <v>ICC 読み込みエラー：{msg}</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC load error: {msg}</v>
+        <v>Could not parse ICC profile: {msg}</v>
       </c>
       <c r="B235" t="str">
-        <v>ICC 読み込みエラー：{msg}</v>
+        <v>ICC プロファイルを解析できませんでした：{msg}</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Could not parse ICC profile: {msg}</v>
+        <v>Popup blocked — allow popups for this site to launch the editor.</v>
       </c>
       <c r="B236" t="str">
-        <v>ICC プロファイルを解析できませんでした：{msg}</v>
+        <v>ポップアップがブロックされました — エディターを起動するにはこのサイトのポップアップを許可してください。</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Popup blocked — allow popups for this site to launch the editor.</v>
+        <v>Failed to load {name}: {msg}</v>
       </c>
       <c r="B237" t="str">
-        <v>ポップアップがブロックされました — エディターを起動するにはこのサイトのポップアップを許可してください。</v>
+        <v>{name} の読み込みに失敗しました：{msg}</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Failed to load {name}: {msg}</v>
+        <v>Color space</v>
       </c>
       <c r="B238" t="str">
-        <v>{name} の読み込みに失敗しました：{msg}</v>
+        <v>色空間</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Color space</v>
+        <v>Device class</v>
       </c>
       <c r="B239" t="str">
-        <v>色空間</v>
+        <v>デバイスクラス</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Device class</v>
+        <v>Colorants</v>
       </c>
       <c r="B240" t="str">
-        <v>デバイスクラス</v>
+        <v>色材</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Colorants</v>
+        <v>Rendering intents</v>
       </c>
       <c r="B241" t="str">
-        <v>色材</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Rendering intents</v>
+        <v>ICC A2B Evaluation</v>
       </c>
       <c r="B242" t="str">
-        <v>レンダリングインテント</v>
+        <v>ICC A2B 評価</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>ICC A2B Evaluation</v>
+        <v>ICC Output</v>
       </c>
       <c r="B243" t="str">
-        <v>ICC A2B 評価</v>
+        <v>ICC 出力</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>ICC Output</v>
+        <v>Image detail</v>
       </c>
       <c r="B244" t="str">
-        <v>ICC 出力</v>
+        <v>画像の精度</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Image detail</v>
+        <v>Coarse</v>
       </c>
       <c r="B245" t="str">
-        <v>画像の精度</v>
+        <v>粗い</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Coarse</v>
+        <v>Standard</v>
       </c>
       <c r="B246" t="str">
-        <v>粗い</v>
+        <v>標準</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Standard</v>
+        <v>Fine</v>
       </c>
       <c r="B247" t="str">
-        <v>標準</v>
+        <v>細かい</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Fine</v>
+        <v>Subscribe</v>
       </c>
       <c r="B248" t="str">
-        <v>細かい</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new chardata releases</v>
       </c>
       <c r="B249" t="str">
-        <v>通知を受け取る</v>
+        <v>chardataの新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Get notified about new chardata releases</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B250" t="str">
-        <v>chardataの新リリース通知を受け取る</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Get notified about new releases</v>
+        <v>Close</v>
       </c>
       <c r="B251" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor chardata release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B252" t="str">
-        <v>閉じる</v>
+        <v>chardataのメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>We’ll email you when a new major or minor chardata release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Email address</v>
       </c>
       <c r="B253" t="str">
-        <v>chardataのメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Email address</v>
+        <v>you@example.com</v>
       </c>
       <c r="B254" t="str">
-        <v>メールアドレス</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>you@example.com</v>
+        <v>How will you use chardata?</v>
       </c>
       <c r="B255" t="str">
-        <v>you@example.com</v>
+        <v>chardataをどのように使いますか？</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>How will you use chardata?</v>
+        <v>(optional)</v>
       </c>
       <c r="B256" t="str">
-        <v>chardataをどのように使いますか？</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>(optional)</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B257" t="str">
-        <v>（任意）</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>I agree to receive emails about chardata releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B258" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>chardataのリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>I agree to receive emails about chardata releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B259" t="str">
-        <v>chardataのリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Subscribe</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B260" t="str">
-        <v>登録</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new chardata release ships.</v>
       </c>
       <c r="B261" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>承認後、ウェルカムメールをお送りします。その後はchardataの新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new chardata release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B262" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後はchardataの新リリース時のみご連絡します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Close</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B263" t="str">
-        <v>閉じる</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Privacy notice</v>
+        <v>Measurement-only data (no device colorants): 3D and 2D-slice point cloud, data table, and label-matched compare are available; gamut shell, extract, tone value, estimate, and validation are disabled.</v>
       </c>
       <c r="B264" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>測定データのみ（デバイス色材なし）：3D および 2D スライスの点群、データ表、ラベル一致比較が利用可能。ガマットシェル、抽出、トーンバリュー、推定、検証は無効です。</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Measurement-only data (no device colorants): 3D and 2D-slice point cloud, data table, and label-matched compare are available; gamut shell, extract, tone value, estimate, and validation are disabled.</v>
+        <v>Sample</v>
       </c>
       <c r="B265" t="str">
-        <v>測定データのみ（デバイス色材なし）：3D および 2D スライスの点群、データ表、ラベル一致比較が利用可能。ガマットシェル、抽出、トーンバリュー、推定、検証は無効です。</v>
+        <v>サンプル</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Sample</v>
+        <v>CxF file is not well-formed XML.</v>
       </c>
       <c r="B266" t="str">
-        <v>サンプル</v>
+        <v>CxF ファイルが整形式 XML ではありません。</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>CxF file is not well-formed XML.</v>
+        <v>CxF file contains no colour objects.</v>
       </c>
       <c r="B267" t="str">
-        <v>CxF ファイルが整形式 XML ではありません。</v>
+        <v>CxF ファイルにカラーオブジェクトが含まれていません。</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>CxF file contains no colour objects.</v>
+        <v>CxF file contains no CIELab or spectral colour values.</v>
       </c>
       <c r="B268" t="str">
-        <v>CxF ファイルにカラーオブジェクトが含まれていません。</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v>CxF file contains no CIELab or spectral colour values.</v>
-      </c>
-      <c r="B269" t="str">
         <v>CxF ファイルに CIELab または分光カラー値が含まれていません。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B269"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B268"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B270"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2551,9 +2551,25 @@
         <v>CxF ファイルに CIELab または分光カラー値が含まれていません。</v>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>IT8.7/5 Patches ({n})</v>
+      </c>
+      <c r="B269" t="str">
+        <v>IT8.7/5 パッチ ({n})</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>Device Patches ({n})</v>
+      </c>
+      <c r="B270" t="str">
+        <v>デバイスパッチ ({n})</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B268"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B270"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B270"/>
+  <dimension ref="A1:B273"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2567,9 +2567,33 @@
         <v>デバイスパッチ ({n})</v>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Number format</v>
+      </c>
+      <c r="B271" t="str">
+        <v>数値形式</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>Hexadecimal</v>
+      </c>
+      <c r="B272" t="str">
+        <v>16 進数</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Decimal</v>
+      </c>
+      <c r="B273" t="str">
+        <v>10 進数</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B270"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B273"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B273"/>
+  <dimension ref="A1:B308"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2591,9 +2591,289 @@
         <v>10 進数</v>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B274" t="str">
+        <v>タグ名</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B275" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B276" t="str">
+        <v>種類</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B277" t="str">
+        <v>オフセット</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B278" t="str">
+        <v>サイズ</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B279" t="str">
+        <v>パディング</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B280" t="str">
+        <v>タグが見つかりません。</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Array of</v>
+      </c>
+      <c r="B281" t="str">
+        <v>配列:</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B282" t="str">
+        <v>プロファイル ID</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B283" t="str">
+        <v>完全な説明を読み込み中…</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v xml:space="preserve">Could not load full description: </v>
+      </c>
+      <c r="B284" t="str">
+        <v xml:space="preserve">完全な説明を読み込めませんでした: </v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B285" t="str">
+        <v>(コンテンツなし)</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Neutral = in gamut</v>
+      </c>
+      <c r="B286" t="str">
+        <v>ニュートラル = 色域内</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Red = out of gamut</v>
+      </c>
+      <c r="B287" t="str">
+        <v>赤 = 色域外</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>No CLUT grid</v>
+      </c>
+      <c r="B288" t="str">
+        <v>CLUT グリッドなし</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Float</v>
+      </c>
+      <c r="B289" t="str">
+        <v>浮動小数点</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Grid</v>
+      </c>
+      <c r="B290" t="str">
+        <v>グリッド</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>PCS → Device</v>
+      </c>
+      <c r="B291" t="str">
+        <v>PCS → デバイス</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>Device → PCS</v>
+      </c>
+      <c r="B292" t="str">
+        <v>デバイス → PCS</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Input</v>
+      </c>
+      <c r="B293" t="str">
+        <v>入力</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Output</v>
+      </c>
+      <c r="B294" t="str">
+        <v>出力</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Human</v>
+      </c>
+      <c r="B295" t="str">
+        <v>実値</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Norm</v>
+      </c>
+      <c r="B296" t="str">
+        <v>正規化</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Chromaticity</v>
+      </c>
+      <c r="B297" t="str">
+        <v>色度</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Tone curve</v>
+      </c>
+      <c r="B298" t="str">
+        <v>トーンカーブ</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>Curve table</v>
+      </c>
+      <c r="B299" t="str">
+        <v>カーブ表</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Scatter</v>
+      </c>
+      <c r="B300" t="str">
+        <v>散布図</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Tables</v>
+      </c>
+      <c r="B301" t="str">
+        <v>テーブル</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Curves</v>
+      </c>
+      <c r="B302" t="str">
+        <v>カーブ</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Input curves</v>
+      </c>
+      <c r="B303" t="str">
+        <v>入力カーブ</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Output curves</v>
+      </c>
+      <c r="B304" t="str">
+        <v>出力カーブ</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>CLUT</v>
+      </c>
+      <c r="B305" t="str">
+        <v>CLUT</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Gamut</v>
+      </c>
+      <c r="B306" t="str">
+        <v>色域</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>Evaluate</v>
+      </c>
+      <c r="B307" t="str">
+        <v>評価</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Data</v>
+      </c>
+      <c r="B308" t="str">
+        <v>データ</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B273"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B308"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B308"/>
+  <dimension ref="A1:B309"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2871,9 +2871,17 @@
         <v>データ</v>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Spot ink characterisation (CxF/X-4): tint levels are loaded as device colorant values; gamut shell, estimate, and model generation are disabled.</v>
+      </c>
+      <c r="B309" t="str">
+        <v>特色インキ特性化（CxF/X-4）：網点パーセントはデバイス色材値として読み込まれます。ガマットシェル、推定、モデル生成は無効です。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B308"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B309"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B309"/>
+  <dimension ref="A1:B310"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2879,9 +2879,17 @@
         <v>特色インキ特性化（CxF/X-4）：網点パーセントはデバイス色材値として読み込まれます。ガマットシェル、推定、モデル生成は無効です。</v>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Reset zoom</v>
+      </c>
+      <c r="B310" t="str">
+        <v>ズームをリセット</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B309"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B310"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B310"/>
+  <dimension ref="A1:B315"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2887,9 +2887,49 @@
         <v>ズームをリセット</v>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>Colorimetry Source</v>
+      </c>
+      <c r="B311" t="str">
+        <v>測色値のソース</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>Prefer spectral</v>
+      </c>
+      <c r="B312" t="str">
+        <v>分光を優先</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>Use file LAB</v>
+      </c>
+      <c r="B313" t="str">
+        <v>ファイルの LAB を使用</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>File has both spectral and LAB; using LAB computed from spectral per preference.</v>
+      </c>
+      <c r="B314" t="str">
+        <v>ファイルに分光と LAB の両方があります。設定に従い分光から算出した LAB を使用します。</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>File has both spectral and LAB; using the file’s LAB per preference.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>ファイルに分光と LAB の両方があります。設定に従いファイルの LAB を使用します。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B310"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B315"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B315"/>
+  <dimension ref="A1:B319"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2927,9 +2927,41 @@
         <v>ファイルに分光と LAB の両方があります。設定に従いファイルの LAB を使用します。</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Zoom in</v>
+      </c>
+      <c r="B316" t="str">
+        <v>拡大</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>Zoom out</v>
+      </c>
+      <c r="B317" t="str">
+        <v>縮小</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>Reset to fit</v>
+      </c>
+      <c r="B318" t="str">
+        <v>フィットにリセット</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>Drag to resize</v>
+      </c>
+      <c r="B319" t="str">
+        <v>ドラッグでサイズ変更</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B315"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B320"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2959,9 +2959,17 @@
         <v>ドラッグでサイズ変更</v>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Show gamut wireframe</v>
+      </c>
+      <c r="B320" t="str">
+        <v>ガマットワイヤーフレームを表示</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B320"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B327"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2967,9 +2967,65 @@
         <v>ガマットワイヤーフレームを表示</v>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Comparison Statistics</v>
+      </c>
+      <c r="B321" t="str">
+        <v>比較統計</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Relative frequency</v>
+      </c>
+      <c r="B322" t="str">
+        <v>相対頻度</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Cumulative frequency</v>
+      </c>
+      <c r="B323" t="str">
+        <v>累積頻度</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Horizontal scale</v>
+      </c>
+      <c r="B324" t="str">
+        <v>横軸スケール</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>Integer ΔE</v>
+      </c>
+      <c r="B325" t="str">
+        <v>整数 ΔE</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>Auto-scale</v>
+      </c>
+      <c r="B326" t="str">
+        <v>自動スケール</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>Bins</v>
+      </c>
+      <c r="B327" t="str">
+        <v>ビン数</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B320"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B327"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B334"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3023,9 +3023,65 @@
         <v>ビン数</v>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Rotation</v>
+      </c>
+      <c r="B328" t="str">
+        <v>回転</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>Mode:</v>
+      </c>
+      <c r="B329" t="str">
+        <v>モード：</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>Turntable</v>
+      </c>
+      <c r="B330" t="str">
+        <v>ターンテーブル</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Orbit</v>
+      </c>
+      <c r="B331" t="str">
+        <v>オービット</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Drag rotate sensitivity:</v>
+      </c>
+      <c r="B332" t="str">
+        <v>ドラッグ回転の感度：</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Enable roll (horizontal scroll)</v>
+      </c>
+      <c r="B333" t="str">
+        <v>ロールを有効化（横スクロール）</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Roll sensitivity:</v>
+      </c>
+      <c r="B334" t="str">
+        <v>ロールの感度：</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B327"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B334"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B334"/>
+  <dimension ref="A1:B377"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3079,9 +3079,353 @@
         <v>ロールの感度：</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Primaries &amp; Overprints</v>
+      </c>
+      <c r="B335" t="str">
+        <v>原色とオーバープリント</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>Patch</v>
+      </c>
+      <c r="B336" t="str">
+        <v>パッチ</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Paper</v>
+      </c>
+      <c r="B337" t="str">
+        <v>用紙</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>Cyan</v>
+      </c>
+      <c r="B338" t="str">
+        <v>シアン</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>Magenta</v>
+      </c>
+      <c r="B339" t="str">
+        <v>マゼンタ</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>Yellow</v>
+      </c>
+      <c r="B340" t="str">
+        <v>イエロー</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>Black</v>
+      </c>
+      <c r="B341" t="str">
+        <v>ブラック</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>Red</v>
+      </c>
+      <c r="B342" t="str">
+        <v>レッド</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Green</v>
+      </c>
+      <c r="B343" t="str">
+        <v>グリーン</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Blue</v>
+      </c>
+      <c r="B344" t="str">
+        <v>ブルー</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>CMY</v>
+      </c>
+      <c r="B345" t="str">
+        <v>CMY</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>CMYK</v>
+      </c>
+      <c r="B346" t="str">
+        <v>CMYK</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Found {n} duplicate measurements in the original dataset.</v>
+      </c>
+      <c r="B347" t="str">
+        <v>元のデータセットで重複測定が {n} 件見つかりました。</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Found {n} duplicate measurements in the original dataset (repeatability ΔE mean {mean}, max {max}).</v>
+      </c>
+      <c r="B348" t="str">
+        <v>元のデータセットで重複測定が {n} 件見つかりました（再現性 ΔE 平均 {mean}、最大 {max}）。</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Near-Neutral Survey</v>
+      </c>
+      <c r="B349" t="str">
+        <v>ニアニュートラル調査</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Threshold (ΔE*ab)</v>
+      </c>
+      <c r="B350" t="str">
+        <v>しきい値 (ΔE*ab)</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>{near} of {total} patches within {thr} ΔE of neutral.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>{total} パッチ中 {near} 個が中性から {thr} ΔE 以内です。</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>No patches within {thr} ΔE of neutral.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>中性から {thr} ΔE 以内のパッチはありません。</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Distance from neutral (ΔE*ab)</v>
+      </c>
+      <c r="B353" t="str">
+        <v>中性からの距離 (ΔE*ab)</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Near-neutral</v>
+      </c>
+      <c r="B354" t="str">
+        <v>ニアニュートラル</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Other patches</v>
+      </c>
+      <c r="B355" t="str">
+        <v>その他のパッチ</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Comparison Plot</v>
+      </c>
+      <c r="B356" t="str">
+        <v>比較プロット</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>P90 = {v}</v>
+      </c>
+      <c r="B357" t="str">
+        <v>P90 = {v}</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Percentiles</v>
+      </c>
+      <c r="B358" t="str">
+        <v>パーセンタイル</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Per-channel ΔE</v>
+      </c>
+      <c r="B359" t="str">
+        <v>チャンネル別 ΔE</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Included: patches using this ink (&gt;0). Excluded: patches without it. Only: this ink alone.</v>
+      </c>
+      <c r="B360" t="str">
+        <v>含む：このインクを使うパッチ（&gt;0）。除く：使わないパッチ。単独：このインクのみ。</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Included</v>
+      </c>
+      <c r="B361" t="str">
+        <v>含む</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Excluded</v>
+      </c>
+      <c r="B362" t="str">
+        <v>除く</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Only</v>
+      </c>
+      <c r="B363" t="str">
+        <v>単独</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>N</v>
+      </c>
+      <c r="B364" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>P90</v>
+      </c>
+      <c r="B365" t="str">
+        <v>P90</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>P95</v>
+      </c>
+      <c r="B366" t="str">
+        <v>P95</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Max</v>
+      </c>
+      <c r="B367" t="str">
+        <v>最大</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="B368" t="str">
+        <v>ユーザーガイド</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Search the guide…</v>
+      </c>
+      <c r="B369" t="str">
+        <v>ガイドを検索…</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Previous match</v>
+      </c>
+      <c r="B370" t="str">
+        <v>前の一致</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Next match</v>
+      </c>
+      <c r="B371" t="str">
+        <v>次の一致</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Open in a new tab</v>
+      </c>
+      <c r="B372" t="str">
+        <v>新しいタブで開く</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>Loading the guide…</v>
+      </c>
+      <c r="B373" t="str">
+        <v>ガイドを読み込み中…</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>Couldn’t load the guide. Try opening it in a new tab.</v>
+      </c>
+      <c r="B374" t="str">
+        <v>ガイドを読み込めませんでした。新しいタブで開いてみてください。</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>No matches</v>
+      </c>
+      <c r="B375" t="str">
+        <v>一致なし</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>{i}/{n}</v>
+      </c>
+      <c r="B376" t="str">
+        <v>{i}/{n}</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>Image is too large to process safely.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>画像が大きすぎるため安全に処理できません。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B334"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B377"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B386"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3423,9 +3423,81 @@
         <v>画像が大きすぎるため安全に処理できません。</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>L* Reversal</v>
+      </c>
+      <c r="B378" t="str">
+        <v>L* 反転</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>Adding ink to a single-ink tint ramp should only darken it. Each measured ramp is checked; any step where L* rises is flagged as a reversal.</v>
+      </c>
+      <c r="B379" t="str">
+        <v>単色インクの階調ランプにインクを追加すると暗くなるだけのはずです。測定した各ランプを検査し、L* が上昇するステップを反転として示します。</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Threshold (ΔL*)</v>
+      </c>
+      <c r="B380" t="str">
+        <v>しきい値 (ΔL*)</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>{n} reversal(s) across {cols} ink ramp(s).</v>
+      </c>
+      <c r="B381" t="str">
+        <v>{cols} 本のインクランプ中 {n} 件の反転。</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>No L* reversals — every ink ramp darkens monotonically.</v>
+      </c>
+      <c r="B382" t="str">
+        <v>L* 反転なし——各インクランプは単調に暗くなります。</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>L* reversal</v>
+      </c>
+      <c r="B383" t="str">
+        <v>L* 反転</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Ink %</v>
+      </c>
+      <c r="B384" t="str">
+        <v>インク %</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Colorant</v>
+      </c>
+      <c r="B385" t="str">
+        <v>色材</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>Ink range</v>
+      </c>
+      <c r="B386" t="str">
+        <v>インク範囲</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B377"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B386"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B398"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3433,10 +3433,10 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Adding ink to a single-ink tint ramp should only darken it. Each measured ramp is checked; any step where L* rises is flagged as a reversal.</v>
+        <v>Adding ink to any one channel should only darken the print — whatever the other inks are set to. Each ink channel is checked against every background of the other inks; any pair where more ink gives a higher L* (a lighter result) is a reversal, flagging a measurement error, ink-limit / trapping artefact, or mislabelled patch.</v>
       </c>
       <c r="B379" t="str">
-        <v>単色インクの階調ランプにインクを追加すると暗くなるだけのはずです。測定した各ランプを検査し、L* が上昇するステップを反転として示します。</v>
+        <v>いずれか1つのチャンネルにインクを追加すると、他のインクの設定にかかわらず、印刷結果は暗くなるだけのはずです。各インクチャンネルは他のインクのあらゆる背景に対して検査され、インクを増やしたのに L* が高くなる（明るくなる）ペアはすべて反転とみなされ、測定誤差、インク制限／トラッピングによるアーティファクト、またはラベル誤りのパッチを示します。</v>
       </c>
     </row>
     <row r="380">
@@ -3449,18 +3449,18 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>{n} reversal(s) across {cols} ink ramp(s).</v>
+        <v>{n} reversal(s) above the threshold across {cols} ink channel(s).</v>
       </c>
       <c r="B381" t="str">
-        <v>{cols} 本のインクランプ中 {n} 件の反転。</v>
+        <v>{cols} 本のインクチャンネルでしきい値を超える反転が {n} 件。</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>No L* reversals — every ink ramp darkens monotonically.</v>
+        <v>No L* reversals above the threshold — every ink darkens monotonically across all backgrounds.</v>
       </c>
       <c r="B382" t="str">
-        <v>L* 反転なし——各インクランプは単調に暗くなります。</v>
+        <v>しきい値を超える L* 反転なし——各インクはすべての背景で単調に暗くなります。</v>
       </c>
     </row>
     <row r="383">
@@ -3495,9 +3495,105 @@
         <v>インク範囲</v>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Channel</v>
+      </c>
+      <c r="B387" t="str">
+        <v>チャンネル</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Ink (low → high)</v>
+      </c>
+      <c r="B388" t="str">
+        <v>インク（低 → 高）</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>All</v>
+      </c>
+      <c r="B389" t="str">
+        <v>すべて</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Show more ({n})</v>
+      </c>
+      <c r="B390" t="str">
+        <v>さらに表示（{n}）</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Per-channel summary</v>
+      </c>
+      <c r="B391" t="str">
+        <v>チャンネル別サマリー</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Samples</v>
+      </c>
+      <c r="B392" t="str">
+        <v>サンプル数</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>Mean ΔL*</v>
+      </c>
+      <c r="B393" t="str">
+        <v>平均 ΔL*</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>SD</v>
+      </c>
+      <c r="B394" t="str">
+        <v>SD</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Max ΔL*</v>
+      </c>
+      <c r="B395" t="str">
+        <v>最大 ΔL*</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v># &gt; ε</v>
+      </c>
+      <c r="B396" t="str">
+        <v># &gt; ε</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>{pts} patches · {ramps} ramps examined · {rev} reversals</v>
+      </c>
+      <c r="B397" t="str">
+        <v>{pts} パッチ · {ramps} ランプ検査 · {rev} 反転</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Channels with many reversals list only the largest {n} by ΔL*.</v>
+      </c>
+      <c r="B398" t="str">
+        <v>反転の多いチャンネルは ΔL* が大きい上位 {n} 件のみ表示します。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B386"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B398"/>
   </ignoredErrors>
 </worksheet>
 </file>